--- a/multi/gpt_realset.xlsx
+++ b/multi/gpt_realset.xlsx
@@ -381,10 +381,10 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
